--- a/SpringCloud以及前沿技术/23_EasyExcel/工作簿WriteDemo2.xlsx
+++ b/SpringCloud以及前沿技术/23_EasyExcel/工作簿WriteDemo2.xlsx
@@ -6,21 +6,37 @@
     <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="模板1" r:id="rId3" sheetId="1"/>
+    <sheet name="模板" r:id="rId3" sheetId="1"/>
   </sheets>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author/>
+  </authors>
+  <commentList>
+    <comment ref="B3" authorId="0">
+      <text>
+        <t>创建批注!</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="0" uniqueCount="0"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-MM-dd HH:mm:ss"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy年MM月dd日HH时mm分ss秒"/>
+    <numFmt numFmtId="165" formatCode="#.##%"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <sz val="11.0"/>
       <color indexed="8"/>
@@ -37,10 +53,6 @@
       <name val="Calibri"/>
       <sz val="11.0"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <sz val="11.0"/>
-    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -96,13 +108,17 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyFont="true"/>
   </cellXfs>
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing"/>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:C11"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
@@ -130,9 +146,9 @@
         </is>
       </c>
       <c r="B2" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C2" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C2" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -143,9 +159,9 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C3" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C3" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -156,9 +172,9 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C4" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C4" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -169,9 +185,9 @@
         </is>
       </c>
       <c r="B5" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C5" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C5" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -182,9 +198,9 @@
         </is>
       </c>
       <c r="B6" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C6" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C6" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -195,9 +211,9 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C7" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C7" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -208,9 +224,9 @@
         </is>
       </c>
       <c r="B8" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C8" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C8" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -221,9 +237,9 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C9" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C9" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -234,9 +250,9 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C10" s="2" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C10" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
@@ -247,143 +263,23 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>45154.80274385417</v>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>字符串0</t>
-        </is>
-      </c>
-      <c r="B12" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C12" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>字符串1</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C13" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>字符串2</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C14" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>字符串3</t>
-        </is>
-      </c>
-      <c r="B15" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>字符串4</t>
-        </is>
-      </c>
-      <c r="B16" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C16" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>字符串5</t>
-        </is>
-      </c>
-      <c r="B17" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C17" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>字符串6</t>
-        </is>
-      </c>
-      <c r="B18" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C18" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>字符串7</t>
-        </is>
-      </c>
-      <c r="B19" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C19" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>字符串8</t>
-        </is>
-      </c>
-      <c r="B20" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C20" t="n">
-        <v>0.56</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>字符串9</t>
-        </is>
-      </c>
-      <c r="B21" s="4" t="n">
-        <v>45154.805746527774</v>
-      </c>
-      <c r="C21" t="n">
+        <v>45154.918768564814</v>
+      </c>
+      <c r="C11" s="4" t="n">
         <v>0.56</v>
       </c>
     </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation type="list" sqref="A2:A3" allowBlank="true" errorStyle="stop">
+      <formula1>"测试1,测试2"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="A1" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId3"/>
 </worksheet>
 </file>